--- a/data/nzd0561/nzd0561.xlsx
+++ b/data/nzd0561/nzd0561.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L499"/>
+  <dimension ref="A1:L500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21378,6 +21378,48 @@
         <v>323.65</v>
       </c>
       <c r="L499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:19+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>409.96</v>
+      </c>
+      <c r="C500" t="n">
+        <v>309.53</v>
+      </c>
+      <c r="D500" t="n">
+        <v>311.35</v>
+      </c>
+      <c r="E500" t="n">
+        <v>322.56</v>
+      </c>
+      <c r="F500" t="n">
+        <v>329.06</v>
+      </c>
+      <c r="G500" t="n">
+        <v>325.61</v>
+      </c>
+      <c r="H500" t="n">
+        <v>324.28</v>
+      </c>
+      <c r="I500" t="n">
+        <v>322.95</v>
+      </c>
+      <c r="J500" t="n">
+        <v>319.64</v>
+      </c>
+      <c r="K500" t="n">
+        <v>322.2</v>
+      </c>
+      <c r="L500" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21394,7 +21436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B518"/>
+  <dimension ref="A1:B519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26577,6 +26619,16 @@
       </c>
       <c r="B518" t="n">
         <v>0.76</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -26745,28 +26797,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.95338297717159</v>
+        <v>2.962264970218259</v>
       </c>
       <c r="J2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K2" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2810944986350696</v>
+        <v>0.2829845332999753</v>
       </c>
       <c r="M2" t="n">
-        <v>30.99424689081135</v>
+        <v>30.96795415158384</v>
       </c>
       <c r="N2" t="n">
-        <v>1349.482621915649</v>
+        <v>1347.904691523999</v>
       </c>
       <c r="O2" t="n">
-        <v>36.73530484310221</v>
+        <v>36.71382153255092</v>
       </c>
       <c r="P2" t="n">
-        <v>306.565769157761</v>
+        <v>306.4741329151286</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26823,28 +26875,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02357597976662444</v>
+        <v>0.02209177798324038</v>
       </c>
       <c r="J3" t="n">
+        <v>499</v>
+      </c>
+      <c r="K3" t="n">
         <v>498</v>
       </c>
-      <c r="K3" t="n">
-        <v>497</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.001754491339299613</v>
+        <v>0.001544747010544967</v>
       </c>
       <c r="M3" t="n">
-        <v>3.399486195258126</v>
+        <v>3.400221036043325</v>
       </c>
       <c r="N3" t="n">
-        <v>19.13551445292137</v>
+        <v>19.1289508517868</v>
       </c>
       <c r="O3" t="n">
-        <v>4.374415898485347</v>
+        <v>4.373665608135446</v>
       </c>
       <c r="P3" t="n">
-        <v>312.8876465508261</v>
+        <v>312.9029309027225</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26901,28 +26953,28 @@
         <v>0.1302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.005857603149579487</v>
+        <v>-0.007707034236285166</v>
       </c>
       <c r="J4" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K4" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001137583765541406</v>
+        <v>0.0001972072848808182</v>
       </c>
       <c r="M4" t="n">
-        <v>3.414855490669918</v>
+        <v>3.417172240043203</v>
       </c>
       <c r="N4" t="n">
-        <v>18.21659487929854</v>
+        <v>18.22943696565568</v>
       </c>
       <c r="O4" t="n">
-        <v>4.268090308240741</v>
+        <v>4.269594473208864</v>
       </c>
       <c r="P4" t="n">
-        <v>316.4887550171956</v>
+        <v>316.5078122286879</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26979,28 +27031,28 @@
         <v>0.1707</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02683641634864</v>
+        <v>-0.02810189286056734</v>
       </c>
       <c r="J5" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K5" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002753364790884505</v>
+        <v>0.003026548206644275</v>
       </c>
       <c r="M5" t="n">
-        <v>3.121891254907366</v>
+        <v>3.121471880512874</v>
       </c>
       <c r="N5" t="n">
-        <v>15.75607249192746</v>
+        <v>15.74760208959281</v>
       </c>
       <c r="O5" t="n">
-        <v>3.969391954938119</v>
+        <v>3.968324846782683</v>
       </c>
       <c r="P5" t="n">
-        <v>326.6894897392792</v>
+        <v>326.702529670153</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27057,28 +27109,28 @@
         <v>0.1817</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04124648870030487</v>
+        <v>-0.0418896573770178</v>
       </c>
       <c r="J6" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K6" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007949578484624631</v>
+        <v>0.008227689510356795</v>
       </c>
       <c r="M6" t="n">
-        <v>2.829118986861949</v>
+        <v>2.826902152639962</v>
       </c>
       <c r="N6" t="n">
-        <v>12.82400603924217</v>
+        <v>12.80427485845361</v>
       </c>
       <c r="O6" t="n">
-        <v>3.581062138422367</v>
+        <v>3.578306143757631</v>
       </c>
       <c r="P6" t="n">
-        <v>331.8984913760648</v>
+        <v>331.9051188203559</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27135,28 +27187,28 @@
         <v>0.1982</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04929361440389655</v>
+        <v>0.04885886280272834</v>
       </c>
       <c r="J7" t="n">
+        <v>499</v>
+      </c>
+      <c r="K7" t="n">
         <v>498</v>
       </c>
-      <c r="K7" t="n">
-        <v>497</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01013319647718192</v>
+        <v>0.009996446328904396</v>
       </c>
       <c r="M7" t="n">
-        <v>3.047468111172222</v>
+        <v>3.044074081180275</v>
       </c>
       <c r="N7" t="n">
-        <v>14.35126802648807</v>
+        <v>14.32518241461056</v>
       </c>
       <c r="O7" t="n">
-        <v>3.788306749259894</v>
+        <v>3.784862271551047</v>
       </c>
       <c r="P7" t="n">
-        <v>325.4530319041745</v>
+        <v>325.457512047126</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27213,28 +27265,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09962833208667907</v>
+        <v>0.0986292174249148</v>
       </c>
       <c r="J8" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K8" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04336364943832272</v>
+        <v>0.04266068658871192</v>
       </c>
       <c r="M8" t="n">
-        <v>3.058980834195813</v>
+        <v>3.058851589750569</v>
       </c>
       <c r="N8" t="n">
-        <v>13.29571963616734</v>
+        <v>13.28338266056091</v>
       </c>
       <c r="O8" t="n">
-        <v>3.646329611563845</v>
+        <v>3.644637521148148</v>
       </c>
       <c r="P8" t="n">
-        <v>324.2914118920979</v>
+        <v>324.3016965496424</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27291,28 +27343,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.180829272310661</v>
+        <v>0.180009742571861</v>
       </c>
       <c r="J9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K9" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1436659328567984</v>
+        <v>0.1429626168069447</v>
       </c>
       <c r="M9" t="n">
-        <v>2.724913803016627</v>
+        <v>2.72464584528377</v>
       </c>
       <c r="N9" t="n">
-        <v>11.81654992810905</v>
+        <v>11.80251232652319</v>
       </c>
       <c r="O9" t="n">
-        <v>3.437520898570516</v>
+        <v>3.435478471264692</v>
       </c>
       <c r="P9" t="n">
-        <v>320.2916377380301</v>
+        <v>320.3000700151932</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27369,28 +27421,28 @@
         <v>0.1446</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07566392451935965</v>
+        <v>0.07531767451399955</v>
       </c>
       <c r="J10" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K10" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01859369110062181</v>
+        <v>0.01850109569549085</v>
       </c>
       <c r="M10" t="n">
-        <v>3.503916750427975</v>
+        <v>3.498849037285165</v>
       </c>
       <c r="N10" t="n">
-        <v>18.3199701285881</v>
+        <v>18.28484732968096</v>
       </c>
       <c r="O10" t="n">
-        <v>4.280183422306584</v>
+        <v>4.276078499008286</v>
       </c>
       <c r="P10" t="n">
-        <v>318.5320635794697</v>
+        <v>318.5356262030997</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27447,28 +27499,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08572106405535475</v>
+        <v>0.08537566944318063</v>
       </c>
       <c r="J11" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K11" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01626471379957839</v>
+        <v>0.01620160025199047</v>
       </c>
       <c r="M11" t="n">
-        <v>4.029964290722686</v>
+        <v>4.023972477960213</v>
       </c>
       <c r="N11" t="n">
-        <v>26.84522409389065</v>
+        <v>26.79314723205174</v>
       </c>
       <c r="O11" t="n">
-        <v>5.181237699033953</v>
+        <v>5.176209736095683</v>
       </c>
       <c r="P11" t="n">
-        <v>320.8252385384347</v>
+        <v>320.8287976103136</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27506,7 +27558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L499"/>
+  <dimension ref="A1:L500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58395,6 +58447,68 @@
         </is>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:19+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-46.77730138042982,168.53034153505348</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-46.77648626889709,168.52931694493597</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-46.77662367242917,168.5284182432381</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-46.776884426465195,168.52755477871946</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-46.7772120920817,168.52675506780704</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-46.77756500407051,168.52600132858254</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-46.777966200807896,168.52530044414556</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>-46.7784310458498,168.52468700235858</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>-46.778936511776784,168.52414231124956</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>-46.779487134346944,168.52372079460847</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0561/nzd0561.xlsx
+++ b/data/nzd0561/nzd0561.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L500"/>
+  <dimension ref="A1:L503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21422,6 +21422,132 @@
       <c r="L500" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-25 22:26:32+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>396.01</v>
+      </c>
+      <c r="C501" t="n">
+        <v>309.18</v>
+      </c>
+      <c r="D501" t="n">
+        <v>311.08</v>
+      </c>
+      <c r="E501" t="n">
+        <v>322.22</v>
+      </c>
+      <c r="F501" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="G501" t="n">
+        <v>324.75</v>
+      </c>
+      <c r="H501" t="n">
+        <v>323.64</v>
+      </c>
+      <c r="I501" t="n">
+        <v>322.15</v>
+      </c>
+      <c r="J501" t="n">
+        <v>318.71</v>
+      </c>
+      <c r="K501" t="n">
+        <v>321.98</v>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>385.18</v>
+      </c>
+      <c r="C502" t="n">
+        <v>308.78</v>
+      </c>
+      <c r="D502" t="n">
+        <v>310.7</v>
+      </c>
+      <c r="E502" t="n">
+        <v>322.12</v>
+      </c>
+      <c r="F502" t="n">
+        <v>328.29</v>
+      </c>
+      <c r="G502" t="n">
+        <v>324.65</v>
+      </c>
+      <c r="H502" t="n">
+        <v>323.64</v>
+      </c>
+      <c r="I502" t="n">
+        <v>322.04</v>
+      </c>
+      <c r="J502" t="n">
+        <v>318</v>
+      </c>
+      <c r="K502" t="n">
+        <v>321.51</v>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:27:02+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>373.56</v>
+      </c>
+      <c r="C503" t="n">
+        <v>308.32</v>
+      </c>
+      <c r="D503" t="n">
+        <v>309.47</v>
+      </c>
+      <c r="E503" t="n">
+        <v>321.56</v>
+      </c>
+      <c r="F503" t="n">
+        <v>328.04</v>
+      </c>
+      <c r="G503" t="n">
+        <v>324.38</v>
+      </c>
+      <c r="H503" t="n">
+        <v>323.47</v>
+      </c>
+      <c r="I503" t="n">
+        <v>321.04</v>
+      </c>
+      <c r="J503" t="n">
+        <v>317.83</v>
+      </c>
+      <c r="K503" t="n">
+        <v>321.23</v>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21436,7 +21562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B519"/>
+  <dimension ref="A1:B522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26629,6 +26755,36 @@
       </c>
       <c r="B519" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-07-25 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -26797,28 +26953,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.962264970218259</v>
+        <v>2.960605101202302</v>
       </c>
       <c r="J2" t="n">
+        <v>502</v>
+      </c>
+      <c r="K2" t="n">
         <v>499</v>
       </c>
-      <c r="K2" t="n">
-        <v>496</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2829845332999753</v>
+        <v>0.2852120268396252</v>
       </c>
       <c r="M2" t="n">
-        <v>30.96795415158384</v>
+        <v>30.83166618224887</v>
       </c>
       <c r="N2" t="n">
-        <v>1347.904691523999</v>
+        <v>1340.325691255492</v>
       </c>
       <c r="O2" t="n">
-        <v>36.71382153255092</v>
+        <v>36.61045876871106</v>
       </c>
       <c r="P2" t="n">
-        <v>306.4741329151286</v>
+        <v>306.4913969986954</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26875,28 +27031,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02209177798324038</v>
+        <v>0.01688091966146649</v>
       </c>
       <c r="J3" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K3" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001544747010544967</v>
+        <v>0.0009075489166369133</v>
       </c>
       <c r="M3" t="n">
-        <v>3.400221036043325</v>
+        <v>3.406205067953777</v>
       </c>
       <c r="N3" t="n">
-        <v>19.1289508517868</v>
+        <v>19.14701277398716</v>
       </c>
       <c r="O3" t="n">
-        <v>4.373665608135446</v>
+        <v>4.375729970414898</v>
       </c>
       <c r="P3" t="n">
-        <v>312.9029309027225</v>
+        <v>312.9567530839241</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26953,28 +27109,28 @@
         <v>0.1302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.007707034236285166</v>
+        <v>-0.01418516329713496</v>
       </c>
       <c r="J4" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K4" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001972072848808182</v>
+        <v>0.0006685410139202208</v>
       </c>
       <c r="M4" t="n">
-        <v>3.417172240043203</v>
+        <v>3.428619019219788</v>
       </c>
       <c r="N4" t="n">
-        <v>18.22943696565568</v>
+        <v>18.32657934023122</v>
       </c>
       <c r="O4" t="n">
-        <v>4.269594473208864</v>
+        <v>4.280955423761291</v>
       </c>
       <c r="P4" t="n">
-        <v>316.5078122286879</v>
+        <v>316.574766435739</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27031,28 +27187,28 @@
         <v>0.1707</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02810189286056734</v>
+        <v>-0.03248342705541038</v>
       </c>
       <c r="J5" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K5" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003026548206644275</v>
+        <v>0.004066190174989326</v>
       </c>
       <c r="M5" t="n">
-        <v>3.121471880512874</v>
+        <v>3.123227938128479</v>
       </c>
       <c r="N5" t="n">
-        <v>15.74760208959281</v>
+        <v>15.74699542635602</v>
       </c>
       <c r="O5" t="n">
-        <v>3.968324846782683</v>
+        <v>3.968248407843947</v>
       </c>
       <c r="P5" t="n">
-        <v>326.702529670153</v>
+        <v>326.7478130139111</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27109,28 +27265,28 @@
         <v>0.1817</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0418896573770178</v>
+        <v>-0.04464093566717089</v>
       </c>
       <c r="J6" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K6" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008227689510356795</v>
+        <v>0.009422753586494581</v>
       </c>
       <c r="M6" t="n">
-        <v>2.826902152639962</v>
+        <v>2.8246579803055</v>
       </c>
       <c r="N6" t="n">
-        <v>12.80427485845361</v>
+        <v>12.76463262238473</v>
       </c>
       <c r="O6" t="n">
-        <v>3.578306143757631</v>
+        <v>3.572762603698254</v>
       </c>
       <c r="P6" t="n">
-        <v>331.9051188203559</v>
+        <v>331.9335535694473</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27187,28 +27343,28 @@
         <v>0.1982</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04885886280272834</v>
+        <v>0.0464572079156243</v>
       </c>
       <c r="J7" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K7" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009996446328904396</v>
+        <v>0.009141230971863035</v>
       </c>
       <c r="M7" t="n">
-        <v>3.044074081180275</v>
+        <v>3.041050109878101</v>
       </c>
       <c r="N7" t="n">
-        <v>14.32518241461056</v>
+        <v>14.26754176264547</v>
       </c>
       <c r="O7" t="n">
-        <v>3.784862271551047</v>
+        <v>3.777239966251213</v>
       </c>
       <c r="P7" t="n">
-        <v>325.457512047126</v>
+        <v>325.4823351831577</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27265,28 +27421,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0986292174249148</v>
+        <v>0.09491112894841941</v>
       </c>
       <c r="J8" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K8" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04266068658871192</v>
+        <v>0.0399107111763789</v>
       </c>
       <c r="M8" t="n">
-        <v>3.058851589750569</v>
+        <v>3.062743844986453</v>
       </c>
       <c r="N8" t="n">
-        <v>13.28338266056091</v>
+        <v>13.27093926385222</v>
       </c>
       <c r="O8" t="n">
-        <v>3.644637521148148</v>
+        <v>3.642930038286794</v>
       </c>
       <c r="P8" t="n">
-        <v>324.3016965496424</v>
+        <v>324.340083551941</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27343,28 +27499,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.180009742571861</v>
+        <v>0.1762567212899436</v>
       </c>
       <c r="J9" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K9" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1429626168069447</v>
+        <v>0.1386544252114742</v>
       </c>
       <c r="M9" t="n">
-        <v>2.72464584528377</v>
+        <v>2.732103263666321</v>
       </c>
       <c r="N9" t="n">
-        <v>11.80251232652319</v>
+        <v>11.80175956719368</v>
       </c>
       <c r="O9" t="n">
-        <v>3.435478471264692</v>
+        <v>3.435368912823437</v>
       </c>
       <c r="P9" t="n">
-        <v>320.3000700151932</v>
+        <v>320.3388033679335</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27421,28 +27577,28 @@
         <v>0.1446</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07531767451399955</v>
+        <v>0.07269119382062295</v>
       </c>
       <c r="J10" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K10" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01850109569549085</v>
+        <v>0.01743555939052432</v>
       </c>
       <c r="M10" t="n">
-        <v>3.498849037285165</v>
+        <v>3.492992220724161</v>
       </c>
       <c r="N10" t="n">
-        <v>18.28484732968096</v>
+        <v>18.20960211369253</v>
       </c>
       <c r="O10" t="n">
-        <v>4.276078499008286</v>
+        <v>4.267271038227186</v>
       </c>
       <c r="P10" t="n">
-        <v>318.5356262030997</v>
+        <v>318.5627334360406</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27499,28 +27655,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08537566944318063</v>
+        <v>0.08366220386541136</v>
       </c>
       <c r="J11" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K11" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01620160025199047</v>
+        <v>0.01575188693344709</v>
       </c>
       <c r="M11" t="n">
-        <v>4.023972477960213</v>
+        <v>4.01020258843828</v>
       </c>
       <c r="N11" t="n">
-        <v>26.79314723205174</v>
+        <v>26.64782913850931</v>
       </c>
       <c r="O11" t="n">
-        <v>5.176209736095683</v>
+        <v>5.162153536898075</v>
       </c>
       <c r="P11" t="n">
-        <v>320.8287976103136</v>
+        <v>320.8465082960179</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27558,7 +27714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L500"/>
+  <dimension ref="A1:L503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58509,6 +58665,192 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-25 22:26:32+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-46.777176587035534,168.53032423338132</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-46.77648314810277,168.5293163758878</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-46.77662128798506,168.52841759019532</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-46.77688151856013,168.527553413978</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-46.77720769459708,168.52675150647403</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-46.777558814180004,168.52599459339942</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-46.77796197139141,168.52529477130852</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>-46.77842645912844,168.52467894449344</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>-46.778931838478066,168.5241322259451</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>-46.779486086403146,168.52371835438294</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-46.77707970442067,168.53031080137131</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-46.77647958148069,168.5293157255471</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-46.77661793210074,168.52841667109817</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-46.77688066329394,168.52755301258352</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-46.77720604554033,168.52675017097428</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-46.77755809442528,168.52599381023867</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-46.77796197139141,168.52529477130852</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>-46.77842582845422,168.5246778365371</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>-46.77892827069031,168.52412452641275</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>-46.77948384761397,168.52371314117417</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:27:02+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-46.77697575465176,168.53029638959606</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-46.776475479865304,168.52931497765533</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-46.77660706963307,168.52841369612656</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-46.776875873803206,168.52755076477442</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-46.777204082377516,168.52674858109376</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-46.77755615108747,168.52599169570482</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-46.77796084795262,168.52529326446134</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>-46.77842009505167,168.52466776420786</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>-46.7789274164312,168.5241226828629</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>-46.7794825138671,168.52371003543297</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0561/nzd0561.xlsx
+++ b/data/nzd0561/nzd0561.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L503"/>
+  <dimension ref="A1:L504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21432,7 +21432,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>396.01</v>
+        <v>409.96</v>
       </c>
       <c r="C501" t="n">
         <v>309.18</v>
@@ -21474,7 +21474,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>385.18</v>
+        <v>409.96</v>
       </c>
       <c r="C502" t="n">
         <v>308.78</v>
@@ -21516,7 +21516,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>373.56</v>
+        <v>409.57</v>
       </c>
       <c r="C503" t="n">
         <v>308.32</v>
@@ -21546,6 +21546,48 @@
         <v>321.23</v>
       </c>
       <c r="L503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:21:00+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>404.63</v>
+      </c>
+      <c r="C504" t="n">
+        <v>306.74</v>
+      </c>
+      <c r="D504" t="n">
+        <v>307.65</v>
+      </c>
+      <c r="E504" t="n">
+        <v>319.59</v>
+      </c>
+      <c r="F504" t="n">
+        <v>325.4</v>
+      </c>
+      <c r="G504" t="n">
+        <v>321.6</v>
+      </c>
+      <c r="H504" t="n">
+        <v>322.7</v>
+      </c>
+      <c r="I504" t="n">
+        <v>320.17</v>
+      </c>
+      <c r="J504" t="n">
+        <v>316.52</v>
+      </c>
+      <c r="K504" t="n">
+        <v>319.78</v>
+      </c>
+      <c r="L504" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -21562,7 +21604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B522"/>
+  <dimension ref="A1:B523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26785,6 +26827,16 @@
       </c>
       <c r="B522" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>
@@ -26953,28 +27005,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.960605101202302</v>
+        <v>2.994505961700051</v>
       </c>
       <c r="J2" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K2" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2852120268396252</v>
+        <v>0.2902221804975595</v>
       </c>
       <c r="M2" t="n">
-        <v>30.83166618224887</v>
+        <v>30.85021895310492</v>
       </c>
       <c r="N2" t="n">
-        <v>1340.325691255492</v>
+        <v>1340.962712898015</v>
       </c>
       <c r="O2" t="n">
-        <v>36.61045876871106</v>
+        <v>36.61915773059253</v>
       </c>
       <c r="P2" t="n">
-        <v>306.4913969986954</v>
+        <v>306.1402413404487</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27031,28 +27083,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01688091966146649</v>
+        <v>0.01443010635375972</v>
       </c>
       <c r="J3" t="n">
+        <v>503</v>
+      </c>
+      <c r="K3" t="n">
         <v>502</v>
       </c>
-      <c r="K3" t="n">
-        <v>501</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0009075489166369133</v>
+        <v>0.0006630289644647958</v>
       </c>
       <c r="M3" t="n">
-        <v>3.406205067953777</v>
+        <v>3.411757614711716</v>
       </c>
       <c r="N3" t="n">
-        <v>19.14701277398716</v>
+        <v>19.19697906553654</v>
       </c>
       <c r="O3" t="n">
-        <v>4.375729970414898</v>
+        <v>4.381435731074523</v>
       </c>
       <c r="P3" t="n">
-        <v>312.9567530839241</v>
+        <v>312.9821722214897</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27109,28 +27161,28 @@
         <v>0.1302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01418516329713496</v>
+        <v>-0.01732458736430971</v>
       </c>
       <c r="J4" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K4" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006685410139202208</v>
+        <v>0.0009932111401816934</v>
       </c>
       <c r="M4" t="n">
-        <v>3.428619019219788</v>
+        <v>3.437556555150395</v>
       </c>
       <c r="N4" t="n">
-        <v>18.32657934023122</v>
+        <v>18.43436440521229</v>
       </c>
       <c r="O4" t="n">
-        <v>4.280955423761291</v>
+        <v>4.293525871030974</v>
       </c>
       <c r="P4" t="n">
-        <v>316.574766435739</v>
+        <v>316.6073469023165</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27187,28 +27239,28 @@
         <v>0.1707</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03248342705541038</v>
+        <v>-0.03479172866519099</v>
       </c>
       <c r="J5" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K5" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004066190174989326</v>
+        <v>0.004658188938819308</v>
       </c>
       <c r="M5" t="n">
-        <v>3.123227938128479</v>
+        <v>3.128100961222649</v>
       </c>
       <c r="N5" t="n">
-        <v>15.74699542635602</v>
+        <v>15.79365603085456</v>
       </c>
       <c r="O5" t="n">
-        <v>3.968248407843947</v>
+        <v>3.97412330342864</v>
       </c>
       <c r="P5" t="n">
-        <v>326.7478130139111</v>
+        <v>326.7717682177444</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27265,28 +27317,28 @@
         <v>0.1817</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04464093566717089</v>
+        <v>-0.04659919415444255</v>
       </c>
       <c r="J6" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K6" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009422753586494581</v>
+        <v>0.01025656995614654</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8246579803055</v>
+        <v>2.829389977333043</v>
       </c>
       <c r="N6" t="n">
-        <v>12.76463262238473</v>
+        <v>12.79536873752026</v>
       </c>
       <c r="O6" t="n">
-        <v>3.572762603698254</v>
+        <v>3.577061466835629</v>
       </c>
       <c r="P6" t="n">
-        <v>331.9335535694473</v>
+        <v>331.9538760788724</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27343,28 +27395,28 @@
         <v>0.1982</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0464572079156243</v>
+        <v>0.04456673917426772</v>
       </c>
       <c r="J7" t="n">
+        <v>503</v>
+      </c>
+      <c r="K7" t="n">
         <v>502</v>
       </c>
-      <c r="K7" t="n">
-        <v>501</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.009141230971863035</v>
+        <v>0.008422612195549073</v>
       </c>
       <c r="M7" t="n">
-        <v>3.041050109878101</v>
+        <v>3.046933655177024</v>
       </c>
       <c r="N7" t="n">
-        <v>14.26754176264547</v>
+        <v>14.29151395242566</v>
       </c>
       <c r="O7" t="n">
-        <v>3.777239966251213</v>
+        <v>3.780411876029603</v>
       </c>
       <c r="P7" t="n">
-        <v>325.4823351831577</v>
+        <v>325.5019559145489</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27421,28 +27473,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09491112894841941</v>
+        <v>0.09336337969515927</v>
       </c>
       <c r="J8" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K8" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0399107111763789</v>
+        <v>0.03872485992913055</v>
       </c>
       <c r="M8" t="n">
-        <v>3.062743844986453</v>
+        <v>3.065818255681964</v>
       </c>
       <c r="N8" t="n">
-        <v>13.27093926385222</v>
+        <v>13.27968721463713</v>
       </c>
       <c r="O8" t="n">
-        <v>3.642930038286794</v>
+        <v>3.644130515587652</v>
       </c>
       <c r="P8" t="n">
-        <v>324.340083551941</v>
+        <v>324.3561307432788</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27499,28 +27551,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1762567212899436</v>
+        <v>0.1744409639085528</v>
       </c>
       <c r="J9" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K9" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1386544252114742</v>
+        <v>0.1362054767764665</v>
       </c>
       <c r="M9" t="n">
-        <v>2.732103263666321</v>
+        <v>2.738086304089063</v>
       </c>
       <c r="N9" t="n">
-        <v>11.80175956719368</v>
+        <v>11.82668477744549</v>
       </c>
       <c r="O9" t="n">
-        <v>3.435368912823437</v>
+        <v>3.438994733558848</v>
       </c>
       <c r="P9" t="n">
-        <v>320.3388033679335</v>
+        <v>320.3576201327492</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27577,28 +27629,28 @@
         <v>0.1446</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07269119382062295</v>
+        <v>0.07121670982476061</v>
       </c>
       <c r="J10" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K10" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01743555939052432</v>
+        <v>0.01678671345486693</v>
       </c>
       <c r="M10" t="n">
-        <v>3.492992220724161</v>
+        <v>3.494487369792561</v>
       </c>
       <c r="N10" t="n">
-        <v>18.20960211369253</v>
+        <v>18.20522552487874</v>
       </c>
       <c r="O10" t="n">
-        <v>4.267271038227186</v>
+        <v>4.266758198548254</v>
       </c>
       <c r="P10" t="n">
-        <v>318.5627334360406</v>
+        <v>318.5780135714039</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27655,28 +27707,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08366220386541136</v>
+        <v>0.08243894475767607</v>
       </c>
       <c r="J11" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K11" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01575188693344709</v>
+        <v>0.0153520495004853</v>
       </c>
       <c r="M11" t="n">
-        <v>4.01020258843828</v>
+        <v>4.009533883756128</v>
       </c>
       <c r="N11" t="n">
-        <v>26.64782913850931</v>
+        <v>26.61674717056527</v>
       </c>
       <c r="O11" t="n">
-        <v>5.162153536898075</v>
+        <v>5.159142096372737</v>
       </c>
       <c r="P11" t="n">
-        <v>320.8465082960179</v>
+        <v>320.8592030934146</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27714,7 +27766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L503"/>
+  <dimension ref="A1:L504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58673,7 +58725,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>-46.777176587035534,168.53032423338132</t>
+          <t>-46.77730138042982,168.53034153505348</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -58735,7 +58787,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>-46.77707970442067,168.53031080137131</t>
+          <t>-46.77730138042982,168.53034153505348</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -58797,7 +58849,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>-46.77697575465176,168.53029638959606</t>
+          <t>-46.777297891582286,168.53034105135</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -58846,6 +58898,68 @@
         </is>
       </c>
       <c r="L503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:21:00+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-46.77725369951308,168.53033492444342</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-46.776461391708075,168.5293124088105</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-46.776590996713324,168.52840929413796</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-46.77685902505878,168.52754285730623</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-46.777183351377,168.52673179196208</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-46.77753614190367,168.5259699238463</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-46.77795575943549,168.52528643933076</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>-46.77841510699081,168.52465900128317</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>-46.77892083361004,168.52410847668673</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>-46.77947560696244,168.52369395213293</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
